--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CodeArdra Solutions\Projects\TSWD.EducationManagementProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F8D9C3-5506-48E7-8DF2-1A61672BA8D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C15874-6261-42DA-ABC4-245C470C40DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9A97B0A3-A67B-4D7F-B785-CC629464B63B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9A97B0A3-A67B-4D7F-B785-CC629464B63B}"/>
   </bookViews>
   <sheets>
     <sheet name="Sprints" sheetId="3" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
   <si>
     <t>ID</t>
   </si>
@@ -140,6 +140,12 @@
   </si>
   <si>
     <t>When Adding new user to tenant (using super master login) its showing unauthrized.</t>
+  </si>
+  <si>
+    <t>Edit Tenant &amp; user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Edit pop up for tenant not opening &amp; for User while editing and saving giving error. </t>
   </si>
 </sst>
 </file>
@@ -207,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -234,11 +240,15 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="25">
     <dxf>
       <font>
         <b/>
@@ -331,6 +341,106 @@
       <fill>
         <patternFill>
           <bgColor theme="3" tint="0.749961851863155"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="3" tint="0.749961851863155"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="8" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.39994506668294322"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="2"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC00000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
     </dxf>
@@ -761,7 +871,7 @@
         <f ca="1">IF($A3&lt; TODAY(),"Overdue",
  IF($A3&lt;=TODAY()+3,"Due Soon",
  "On Track"))</f>
-        <v>Due Soon</v>
+        <v>Overdue</v>
       </c>
     </row>
   </sheetData>
@@ -906,19 +1016,35 @@
         <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A4" s="7"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="4"/>
+    <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>16</v>
+      </c>
       <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="G4" s="10">
+        <v>46081</v>
+      </c>
+      <c r="H4" s="7">
+        <v>8</v>
+      </c>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
+      <c r="L4" s="11" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="7"/>
@@ -1272,50 +1398,53 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="11" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
       <formula>"Task"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
+      <formula>"Bug"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="10" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
       <formula>"Low"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="9" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
       <formula>"Medium"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="8" operator="equal">
       <formula>"High"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="cellIs" dxfId="7" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="9" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
       <formula>"On Hold"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E2:E3">
-    <cfRule type="cellIs" dxfId="5" priority="11" operator="equal">
+  <conditionalFormatting sqref="E2:E4">
+    <cfRule type="cellIs" dxfId="19" priority="12" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E5">
-    <cfRule type="cellIs" dxfId="4" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1048576">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="16" priority="2">
       <formula>$G2&gt;TODAY()+3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>AND($G2&gt;=TODAY(), $G2&lt;=TODAY()+3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="3">
+    <cfRule type="expression" dxfId="14" priority="4">
       <formula>AND($G2&lt;TODAY(), $G2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1334,7 +1463,7 @@
           <x14:formula1>
             <xm:f>Lists!B:B</xm:f>
           </x14:formula1>
-          <xm:sqref>C1:D3</xm:sqref>
+          <xm:sqref>C1:D3 C4</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -8,14 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CodeArdra Solutions\Projects\TSWD.EducationManagementProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1C15874-6261-42DA-ABC4-245C470C40DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94024493-15DB-4951-8957-BCB86B012730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{9A97B0A3-A67B-4D7F-B785-CC629464B63B}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9A97B0A3-A67B-4D7F-B785-CC629464B63B}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sprints" sheetId="3" r:id="rId1"/>
-    <sheet name="Tasks" sheetId="1" r:id="rId2"/>
-    <sheet name="Lists" sheetId="2" state="hidden" r:id="rId3"/>
+    <sheet name="Tasks" sheetId="1" r:id="rId1"/>
+    <sheet name="Lists" sheetId="2" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="32">
   <si>
     <t>ID</t>
   </si>
@@ -122,18 +121,6 @@
   </si>
   <si>
     <t>Handle the logic: AppSchoolRules have Rule Name{Attendance, Percentage, etc}. AppFilter have filters optin like &gt;, &lt;, == etc. AppPromotionRules have Rules required for promotions like Attandance &gt; 75%. AppClasses have the classes of school. AppSections is sections of classes. AppSubjects have the subject releted to classes</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Task ID</t>
-  </si>
-  <si>
-    <t>Hours Worked</t>
-  </si>
-  <si>
-    <t>Deadline Status</t>
   </si>
   <si>
     <t>Tenat User Creation</t>
@@ -152,9 +139,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -213,17 +197,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -237,9 +212,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -248,7 +220,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="13">
     <dxf>
       <font>
         <b/>
@@ -348,101 +320,6 @@
       <font>
         <color rgb="FFFF0000"/>
       </font>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="3" tint="0.749961851863155"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="8" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="2"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -778,120 +655,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2090EB5-616E-432C-BC93-8F7FD8C0E8C6}">
-  <dimension ref="A1:H3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="25.88671875" customWidth="1"/>
-    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5546875" customWidth="1"/>
-    <col min="6" max="6" width="28.77734375" customWidth="1"/>
-    <col min="7" max="7" width="5.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="26.21875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="H1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="3">
-        <v>46054</v>
-      </c>
-      <c r="B2" s="2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="2" t="str">
-        <f>IF(B2="","",VLOOKUP(B2,Tasks!A:Z,2,FALSE))</f>
-        <v>School Academic Rules</v>
-      </c>
-      <c r="D2" s="2">
-        <v>4</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" s="9">
-        <f>IF(B2="","",VLOOKUP(B2,Tasks!A:G,7,FALSE))</f>
-        <v>46081</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" t="str">
-        <f ca="1">IF($F2&lt; TODAY(),"Overdue",
- IF($F2&lt;=TODAY()+3,"Due Soon",
- "On Track"))</f>
-        <v>On Track</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="3">
-        <v>46076</v>
-      </c>
-      <c r="B3" s="2">
-        <v>2</v>
-      </c>
-      <c r="C3" s="2" t="str">
-        <f>IF(B3="","",VLOOKUP(B3,Tasks!A:Z,2,FALSE))</f>
-        <v>Tenat User Creation</v>
-      </c>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="9">
-        <f>IF(B3="","",VLOOKUP(B3,Tasks!A:G,7,FALSE))</f>
-        <v>46081</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" t="str">
-        <f ca="1">IF($A3&lt; TODAY(),"Overdue",
- IF($A3&lt;=TODAY()+3,"Due Soon",
- "On Track"))</f>
-        <v>Overdue</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{02ACE3A6-6A4D-4CE7-A895-73B928FF3F99}">
-          <x14:formula1>
-            <xm:f>Tasks!A:A</xm:f>
-          </x14:formula1>
-          <xm:sqref>B1:B1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F057502-807C-4919-BF6B-5E704F78B6DB}">
   <dimension ref="A1:L29"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -911,540 +674,548 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="K1" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="L1" s="5" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="91.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="A2" s="1">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="2">
         <v>46054</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="2">
         <v>46081</v>
       </c>
-      <c r="H2" s="4">
+      <c r="H2" s="1">
         <v>6</v>
       </c>
-      <c r="I2" s="4">
+      <c r="I2" s="1">
         <v>0</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="3">
         <v>0.1</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="1" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5">
+      <c r="E3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46076</v>
+      </c>
+      <c r="G3" s="2">
         <v>46081</v>
       </c>
-      <c r="H3" s="4">
+      <c r="H3" s="1">
         <v>3</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="4" t="s">
-        <v>33</v>
+      <c r="I3" s="1">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="7">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="4" t="s">
+      <c r="B4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="10">
+      <c r="E4" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46077</v>
+      </c>
+      <c r="G4" s="6">
         <v>46081</v>
       </c>
-      <c r="H4" s="7">
-        <v>8</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="11" t="s">
-        <v>35</v>
+      <c r="H4" s="4">
+        <v>1</v>
+      </c>
+      <c r="I4" s="4">
+        <v>1</v>
+      </c>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A5" s="7"/>
-      <c r="B5" s="7"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="7"/>
-      <c r="K5" s="7"/>
-      <c r="L5" s="7"/>
+      <c r="A5" s="4"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="4"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="4"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A6" s="7"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
+      <c r="A6" s="4"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="4"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="4"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
+      <c r="A7" s="4"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+      <c r="L7" s="4"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="4"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="4"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="4"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
+      <c r="A9" s="4"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="4"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="4"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="4"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="4"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="4"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="4"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="4"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="4"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="4"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
+      <c r="A12" s="4"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="4"/>
+      <c r="E12" s="4"/>
+      <c r="F12" s="4"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4"/>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4"/>
+      <c r="L12" s="4"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
+      <c r="A13" s="4"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="4"/>
+      <c r="E13" s="4"/>
+      <c r="F13" s="4"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4"/>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4"/>
+      <c r="L13" s="4"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
+      <c r="A14" s="4"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="4"/>
+      <c r="E14" s="4"/>
+      <c r="F14" s="4"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+      <c r="L14" s="4"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="4"/>
+      <c r="F15" s="4"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="4"/>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+      <c r="L15" s="4"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="4"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="4"/>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+      <c r="L16" s="4"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+      <c r="L17" s="4"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="4"/>
+      <c r="F18" s="4"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="4"/>
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
+      <c r="L18" s="4"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
+      <c r="A19" s="4"/>
+      <c r="B19" s="4"/>
+      <c r="C19" s="4"/>
+      <c r="D19" s="4"/>
+      <c r="E19" s="4"/>
+      <c r="F19" s="4"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="4"/>
+      <c r="I19" s="4"/>
+      <c r="J19" s="4"/>
+      <c r="K19" s="4"/>
+      <c r="L19" s="4"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="7"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
+      <c r="A20" s="4"/>
+      <c r="B20" s="4"/>
+      <c r="C20" s="4"/>
+      <c r="D20" s="4"/>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="4"/>
+      <c r="I20" s="4"/>
+      <c r="J20" s="4"/>
+      <c r="K20" s="4"/>
+      <c r="L20" s="4"/>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A21" s="7"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
+      <c r="A21" s="4"/>
+      <c r="B21" s="4"/>
+      <c r="C21" s="4"/>
+      <c r="D21" s="4"/>
+      <c r="E21" s="4"/>
+      <c r="F21" s="4"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="4"/>
+      <c r="I21" s="4"/>
+      <c r="J21" s="4"/>
+      <c r="K21" s="4"/>
+      <c r="L21" s="4"/>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-      <c r="H22" s="7"/>
-      <c r="I22" s="7"/>
-      <c r="J22" s="7"/>
-      <c r="K22" s="7"/>
-      <c r="L22" s="7"/>
+      <c r="A22" s="4"/>
+      <c r="B22" s="4"/>
+      <c r="C22" s="4"/>
+      <c r="D22" s="4"/>
+      <c r="E22" s="4"/>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+      <c r="K22" s="4"/>
+      <c r="L22" s="4"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A23" s="7"/>
-      <c r="B23" s="7"/>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-      <c r="I23" s="7"/>
-      <c r="J23" s="7"/>
-      <c r="K23" s="7"/>
-      <c r="L23" s="7"/>
+      <c r="A23" s="4"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="7"/>
-      <c r="D24" s="7"/>
-      <c r="E24" s="7"/>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
-      <c r="I24" s="7"/>
-      <c r="J24" s="7"/>
-      <c r="K24" s="7"/>
-      <c r="L24" s="7"/>
+      <c r="A24" s="4"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A25" s="7"/>
-      <c r="B25" s="7"/>
-      <c r="C25" s="7"/>
-      <c r="D25" s="7"/>
-      <c r="E25" s="7"/>
-      <c r="F25" s="7"/>
-      <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
-      <c r="I25" s="7"/>
-      <c r="J25" s="7"/>
-      <c r="K25" s="7"/>
-      <c r="L25" s="7"/>
+      <c r="A25" s="4"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+      <c r="E25" s="4"/>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4"/>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4"/>
+      <c r="L25" s="4"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="7"/>
-      <c r="D26" s="7"/>
-      <c r="E26" s="7"/>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-      <c r="H26" s="7"/>
-      <c r="I26" s="7"/>
-      <c r="J26" s="7"/>
-      <c r="K26" s="7"/>
-      <c r="L26" s="7"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+      <c r="E26" s="4"/>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4"/>
+      <c r="I26" s="4"/>
+      <c r="J26" s="4"/>
+      <c r="K26" s="4"/>
+      <c r="L26" s="4"/>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A27" s="7"/>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="7"/>
-      <c r="G27" s="7"/>
-      <c r="H27" s="7"/>
-      <c r="I27" s="7"/>
-      <c r="J27" s="7"/>
-      <c r="K27" s="7"/>
-      <c r="L27" s="7"/>
+      <c r="A27" s="4"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+      <c r="E27" s="4"/>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4"/>
+      <c r="I27" s="4"/>
+      <c r="J27" s="4"/>
+      <c r="K27" s="4"/>
+      <c r="L27" s="4"/>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-      <c r="H28" s="7"/>
-      <c r="I28" s="7"/>
-      <c r="J28" s="7"/>
-      <c r="K28" s="7"/>
-      <c r="L28" s="7"/>
+      <c r="A28" s="4"/>
+      <c r="B28" s="4"/>
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+      <c r="E28" s="4"/>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4"/>
+      <c r="I28" s="4"/>
+      <c r="J28" s="4"/>
+      <c r="K28" s="4"/>
+      <c r="L28" s="4"/>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A29" s="7"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="7"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="7"/>
-      <c r="H29" s="7"/>
-      <c r="I29" s="7"/>
-      <c r="J29" s="7"/>
-      <c r="K29" s="7"/>
-      <c r="L29" s="7"/>
+      <c r="A29" s="4"/>
+      <c r="B29" s="4"/>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4"/>
+      <c r="I29" s="4"/>
+      <c r="J29" s="4"/>
+      <c r="K29" s="4"/>
+      <c r="L29" s="4"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
-      <formula>"Task"</formula>
-    </cfRule>
     <cfRule type="cellIs" dxfId="12" priority="1" operator="equal">
       <formula>"Bug"</formula>
     </cfRule>
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+      <formula>"Task"</formula>
+    </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D1048576">
-    <cfRule type="cellIs" dxfId="24" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
       <formula>"Low"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="23" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="7" operator="equal">
       <formula>"Medium"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="8" operator="equal">
       <formula>"High"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1:E1048576">
-    <cfRule type="cellIs" dxfId="21" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
       <formula>"Blocked"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
       <formula>"On Hold"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E4">
-    <cfRule type="cellIs" dxfId="19" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="12" operator="equal">
       <formula>"Done"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E2:E5">
-    <cfRule type="cellIs" dxfId="18" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
       <formula>"In Progress"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="17" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="13" operator="equal">
       <formula>"Not Started"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G2:G1048576">
-    <cfRule type="expression" dxfId="16" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>$G2&gt;TODAY()+3</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="15" priority="3">
+    <cfRule type="expression" dxfId="1" priority="3">
       <formula>AND($G2&gt;=TODAY(), $G2&lt;=TODAY()+3)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="4">
+    <cfRule type="expression" dxfId="0" priority="4">
       <formula>AND($G2&lt;TODAY(), $G2&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1471,7 +1242,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{157724B3-0314-4773-B1BD-9577D4FB097B}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/Tasks.xlsx
+++ b/Tasks.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\CodeArdra Solutions\Projects\TSWD.EducationManagementProject\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94024493-15DB-4951-8957-BCB86B012730}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5624422-2E97-4BB3-9CEB-1319736663F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{9A97B0A3-A67B-4D7F-B785-CC629464B63B}"/>
   </bookViews>
